--- a/artfynd/A 29537-2025 artfynd.xlsx
+++ b/artfynd/A 29537-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89046626</v>
+        <v>89046634</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skårelflyn, V om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522030.1744198659</v>
+        <v>521982</v>
       </c>
       <c r="R2" t="n">
-        <v>7036324.174917114</v>
+        <v>7036453</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +752,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +768,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gammal barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
+          <t>svagt kalkpåverkad, ca 140-årig granskog</t>
+        </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov granhögstubbe</t>
+          <t>i komposterad barrmatta i kanten av aktiv myrstack</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,12 +798,7 @@
         <v>89046627</v>
       </c>
       <c r="B3" t="n">
-        <v>88943</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +820,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -853,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521970.131527216</v>
+        <v>521970</v>
       </c>
       <c r="R3" t="n">
-        <v>7036326.892659458</v>
+        <v>7036327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,19 +872,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,6 +903,120 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89046626</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skårelflyn, V om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>522030</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7036324</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 29537-2025 artfynd.xlsx
+++ b/artfynd/A 29537-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046634</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046627</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,8 +1036,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046626</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>